--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205214</v>
+        <v>123205205</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500156</v>
+        <v>500249</v>
       </c>
       <c r="R2" t="n">
-        <v>6998001</v>
+        <v>6997921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205215</v>
+        <v>123205199</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500160</v>
+        <v>500157</v>
       </c>
       <c r="R3" t="n">
-        <v>6997999</v>
+        <v>6997979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205211</v>
+        <v>123205207</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500162</v>
+        <v>500272</v>
       </c>
       <c r="R4" t="n">
-        <v>6998023</v>
+        <v>6997930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205204</v>
+        <v>123205208</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500241</v>
+        <v>500289</v>
       </c>
       <c r="R5" t="n">
-        <v>6997932</v>
+        <v>6997933</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205217</v>
+        <v>123205213</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499997</v>
+        <v>500152</v>
       </c>
       <c r="R6" t="n">
-        <v>6997980</v>
+        <v>6998004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205202</v>
+        <v>123205214</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500189</v>
+        <v>500156</v>
       </c>
       <c r="R7" t="n">
-        <v>6997952</v>
+        <v>6998001</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205213</v>
+        <v>123205206</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500152</v>
+        <v>500253</v>
       </c>
       <c r="R8" t="n">
-        <v>6998004</v>
+        <v>6997934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205198</v>
+        <v>123205209</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500158</v>
+        <v>500274</v>
       </c>
       <c r="R9" t="n">
-        <v>6997989</v>
+        <v>6997998</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205208</v>
+        <v>123205215</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500289</v>
+        <v>500160</v>
       </c>
       <c r="R10" t="n">
-        <v>6997933</v>
+        <v>6997999</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205199</v>
+        <v>123205211</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500157</v>
+        <v>500162</v>
       </c>
       <c r="R11" t="n">
-        <v>6997979</v>
+        <v>6998023</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205206</v>
+        <v>123205203</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500253</v>
+        <v>500221</v>
       </c>
       <c r="R12" t="n">
-        <v>6997934</v>
+        <v>6997968</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205207</v>
+        <v>123205202</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500272</v>
+        <v>500189</v>
       </c>
       <c r="R13" t="n">
-        <v>6997930</v>
+        <v>6997952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205209</v>
+        <v>123205210</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500274</v>
+        <v>500157</v>
       </c>
       <c r="R14" t="n">
-        <v>6997998</v>
+        <v>6998027</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205203</v>
+        <v>123205201</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500221</v>
+        <v>500163</v>
       </c>
       <c r="R15" t="n">
-        <v>6997968</v>
+        <v>6997976</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205201</v>
+        <v>123205198</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500163</v>
+        <v>500158</v>
       </c>
       <c r="R16" t="n">
-        <v>6997976</v>
+        <v>6997989</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205205</v>
+        <v>123205204</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500249</v>
+        <v>500241</v>
       </c>
       <c r="R17" t="n">
-        <v>6997921</v>
+        <v>6997932</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205210</v>
+        <v>123205217</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500157</v>
+        <v>499997</v>
       </c>
       <c r="R18" t="n">
-        <v>6998027</v>
+        <v>6997980</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205211</v>
+        <v>123205202</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500162</v>
+        <v>500189</v>
       </c>
       <c r="R11" t="n">
-        <v>6998023</v>
+        <v>6997952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205203</v>
+        <v>123205211</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500221</v>
+        <v>500162</v>
       </c>
       <c r="R12" t="n">
-        <v>6997968</v>
+        <v>6998023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205202</v>
+        <v>123205203</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500189</v>
+        <v>500221</v>
       </c>
       <c r="R13" t="n">
-        <v>6997952</v>
+        <v>6997968</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205202</v>
+        <v>123205211</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500189</v>
+        <v>500162</v>
       </c>
       <c r="R11" t="n">
-        <v>6997952</v>
+        <v>6998023</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205211</v>
+        <v>123205203</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500162</v>
+        <v>500221</v>
       </c>
       <c r="R12" t="n">
-        <v>6998023</v>
+        <v>6997968</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205203</v>
+        <v>123205202</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500221</v>
+        <v>500189</v>
       </c>
       <c r="R13" t="n">
-        <v>6997968</v>
+        <v>6997952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205199</v>
+        <v>123205207</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500157</v>
+        <v>500272</v>
       </c>
       <c r="R3" t="n">
-        <v>6997979</v>
+        <v>6997930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205207</v>
+        <v>123205198</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500272</v>
+        <v>500158</v>
       </c>
       <c r="R4" t="n">
-        <v>6997930</v>
+        <v>6997989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205208</v>
+        <v>123205206</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500289</v>
+        <v>500253</v>
       </c>
       <c r="R5" t="n">
-        <v>6997933</v>
+        <v>6997934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205213</v>
+        <v>123205202</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500152</v>
+        <v>500189</v>
       </c>
       <c r="R6" t="n">
-        <v>6998004</v>
+        <v>6997952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205214</v>
+        <v>123205212</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500156</v>
+        <v>500164</v>
       </c>
       <c r="R7" t="n">
-        <v>6998001</v>
+        <v>6998017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205206</v>
+        <v>123205208</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500253</v>
+        <v>500289</v>
       </c>
       <c r="R8" t="n">
-        <v>6997934</v>
+        <v>6997933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205209</v>
+        <v>123205201</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500274</v>
+        <v>500163</v>
       </c>
       <c r="R9" t="n">
-        <v>6997998</v>
+        <v>6997976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205215</v>
+        <v>123205214</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500160</v>
+        <v>500156</v>
       </c>
       <c r="R10" t="n">
-        <v>6997999</v>
+        <v>6998001</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205211</v>
+        <v>123205199</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500162</v>
+        <v>500157</v>
       </c>
       <c r="R11" t="n">
-        <v>6998023</v>
+        <v>6997979</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205203</v>
+        <v>123205204</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500221</v>
+        <v>500241</v>
       </c>
       <c r="R12" t="n">
-        <v>6997968</v>
+        <v>6997932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205202</v>
+        <v>123205203</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500189</v>
+        <v>500221</v>
       </c>
       <c r="R13" t="n">
-        <v>6997952</v>
+        <v>6997968</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205210</v>
+        <v>123205213</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500157</v>
+        <v>500152</v>
       </c>
       <c r="R14" t="n">
-        <v>6998027</v>
+        <v>6998004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205201</v>
+        <v>123205209</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500163</v>
+        <v>500274</v>
       </c>
       <c r="R15" t="n">
-        <v>6997976</v>
+        <v>6997998</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205198</v>
+        <v>123205211</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500158</v>
+        <v>500162</v>
       </c>
       <c r="R16" t="n">
-        <v>6997989</v>
+        <v>6998023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205204</v>
+        <v>123205217</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500241</v>
+        <v>499997</v>
       </c>
       <c r="R17" t="n">
-        <v>6997932</v>
+        <v>6997980</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205217</v>
+        <v>123205210</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>499997</v>
+        <v>500157</v>
       </c>
       <c r="R18" t="n">
-        <v>6997980</v>
+        <v>6998027</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205212</v>
+        <v>123205215</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500164</v>
+        <v>500160</v>
       </c>
       <c r="R19" t="n">
-        <v>6998017</v>
+        <v>6997999</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205205</v>
+        <v>123205208</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500249</v>
+        <v>500289</v>
       </c>
       <c r="R2" t="n">
-        <v>6997921</v>
+        <v>6997933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205207</v>
+        <v>123205217</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500272</v>
+        <v>499997</v>
       </c>
       <c r="R3" t="n">
-        <v>6997930</v>
+        <v>6997980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205198</v>
+        <v>123205206</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500158</v>
+        <v>500253</v>
       </c>
       <c r="R4" t="n">
-        <v>6997989</v>
+        <v>6997934</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205206</v>
+        <v>123205203</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500253</v>
+        <v>500221</v>
       </c>
       <c r="R5" t="n">
-        <v>6997934</v>
+        <v>6997968</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205202</v>
+        <v>123205214</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500189</v>
+        <v>500156</v>
       </c>
       <c r="R6" t="n">
-        <v>6997952</v>
+        <v>6998001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205212</v>
+        <v>123205202</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500164</v>
+        <v>500189</v>
       </c>
       <c r="R7" t="n">
-        <v>6998017</v>
+        <v>6997952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205208</v>
+        <v>123205215</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500289</v>
+        <v>500160</v>
       </c>
       <c r="R8" t="n">
-        <v>6997933</v>
+        <v>6997999</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205201</v>
+        <v>123205212</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500163</v>
+        <v>500164</v>
       </c>
       <c r="R9" t="n">
-        <v>6997976</v>
+        <v>6998017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205214</v>
+        <v>123205201</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500156</v>
+        <v>500163</v>
       </c>
       <c r="R10" t="n">
-        <v>6998001</v>
+        <v>6997976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205199</v>
+        <v>123205213</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500157</v>
+        <v>500152</v>
       </c>
       <c r="R11" t="n">
-        <v>6997979</v>
+        <v>6998004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205204</v>
+        <v>123205199</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500241</v>
+        <v>500157</v>
       </c>
       <c r="R12" t="n">
-        <v>6997932</v>
+        <v>6997979</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205203</v>
+        <v>123205204</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500221</v>
+        <v>500241</v>
       </c>
       <c r="R13" t="n">
-        <v>6997968</v>
+        <v>6997932</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205213</v>
+        <v>123205205</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500152</v>
+        <v>500249</v>
       </c>
       <c r="R14" t="n">
-        <v>6998004</v>
+        <v>6997921</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205209</v>
+        <v>123205210</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500274</v>
+        <v>500157</v>
       </c>
       <c r="R15" t="n">
-        <v>6997998</v>
+        <v>6998027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205211</v>
+        <v>123205209</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500162</v>
+        <v>500274</v>
       </c>
       <c r="R16" t="n">
-        <v>6998023</v>
+        <v>6997998</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205217</v>
+        <v>123205211</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>499997</v>
+        <v>500162</v>
       </c>
       <c r="R17" t="n">
-        <v>6997980</v>
+        <v>6998023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205210</v>
+        <v>123205198</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500157</v>
+        <v>500158</v>
       </c>
       <c r="R18" t="n">
-        <v>6998027</v>
+        <v>6997989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205215</v>
+        <v>123205207</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500160</v>
+        <v>500272</v>
       </c>
       <c r="R19" t="n">
-        <v>6997999</v>
+        <v>6997930</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205208</v>
+        <v>123205203</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500289</v>
+        <v>500221</v>
       </c>
       <c r="R2" t="n">
-        <v>6997933</v>
+        <v>6997968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205217</v>
+        <v>123205205</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499997</v>
+        <v>500249</v>
       </c>
       <c r="R3" t="n">
-        <v>6997980</v>
+        <v>6997921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205206</v>
+        <v>123205201</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500253</v>
+        <v>500163</v>
       </c>
       <c r="R4" t="n">
-        <v>6997934</v>
+        <v>6997976</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205203</v>
+        <v>123205215</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500221</v>
+        <v>500160</v>
       </c>
       <c r="R5" t="n">
-        <v>6997968</v>
+        <v>6997999</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205214</v>
+        <v>123205211</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500156</v>
+        <v>500162</v>
       </c>
       <c r="R6" t="n">
-        <v>6998001</v>
+        <v>6998023</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205202</v>
+        <v>123205210</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500189</v>
+        <v>500157</v>
       </c>
       <c r="R7" t="n">
-        <v>6997952</v>
+        <v>6998027</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205215</v>
+        <v>123205214</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500160</v>
+        <v>500156</v>
       </c>
       <c r="R8" t="n">
-        <v>6997999</v>
+        <v>6998001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205212</v>
+        <v>123205207</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500164</v>
+        <v>500272</v>
       </c>
       <c r="R9" t="n">
-        <v>6998017</v>
+        <v>6997930</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205201</v>
+        <v>123205213</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500163</v>
+        <v>500152</v>
       </c>
       <c r="R10" t="n">
-        <v>6997976</v>
+        <v>6998004</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205213</v>
+        <v>123205198</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500152</v>
+        <v>500158</v>
       </c>
       <c r="R11" t="n">
-        <v>6998004</v>
+        <v>6997989</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205199</v>
+        <v>123205202</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500157</v>
+        <v>500189</v>
       </c>
       <c r="R12" t="n">
-        <v>6997979</v>
+        <v>6997952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205204</v>
+        <v>123205217</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500241</v>
+        <v>499997</v>
       </c>
       <c r="R13" t="n">
-        <v>6997932</v>
+        <v>6997980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205205</v>
+        <v>123205209</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500249</v>
+        <v>500274</v>
       </c>
       <c r="R14" t="n">
-        <v>6997921</v>
+        <v>6997998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205210</v>
+        <v>123205199</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>500157</v>
       </c>
       <c r="R15" t="n">
-        <v>6998027</v>
+        <v>6997979</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205209</v>
+        <v>123205212</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500274</v>
+        <v>500164</v>
       </c>
       <c r="R16" t="n">
-        <v>6997998</v>
+        <v>6998017</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205211</v>
+        <v>123205208</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500162</v>
+        <v>500289</v>
       </c>
       <c r="R17" t="n">
-        <v>6998023</v>
+        <v>6997933</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205198</v>
+        <v>123205206</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500158</v>
+        <v>500253</v>
       </c>
       <c r="R18" t="n">
-        <v>6997989</v>
+        <v>6997934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205207</v>
+        <v>123205204</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500272</v>
+        <v>500241</v>
       </c>
       <c r="R19" t="n">
-        <v>6997930</v>
+        <v>6997932</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205203</v>
+        <v>123205206</v>
       </c>
       <c r="B2" t="n">
         <v>57481</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500221</v>
+        <v>500253</v>
       </c>
       <c r="R2" t="n">
-        <v>6997968</v>
+        <v>6997934</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205205</v>
+        <v>123205203</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500249</v>
+        <v>500221</v>
       </c>
       <c r="R3" t="n">
-        <v>6997921</v>
+        <v>6997968</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205201</v>
+        <v>123205198</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500163</v>
+        <v>500158</v>
       </c>
       <c r="R4" t="n">
-        <v>6997976</v>
+        <v>6997989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205215</v>
+        <v>123205208</v>
       </c>
       <c r="B5" t="n">
         <v>57481</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500160</v>
+        <v>500289</v>
       </c>
       <c r="R5" t="n">
-        <v>6997999</v>
+        <v>6997933</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205211</v>
+        <v>123205205</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500162</v>
+        <v>500249</v>
       </c>
       <c r="R6" t="n">
-        <v>6998023</v>
+        <v>6997921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205210</v>
+        <v>123205202</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500157</v>
+        <v>500189</v>
       </c>
       <c r="R7" t="n">
-        <v>6998027</v>
+        <v>6997952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205214</v>
+        <v>123205217</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500156</v>
+        <v>499997</v>
       </c>
       <c r="R8" t="n">
-        <v>6998001</v>
+        <v>6997980</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205207</v>
+        <v>123205204</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500272</v>
+        <v>500241</v>
       </c>
       <c r="R9" t="n">
-        <v>6997930</v>
+        <v>6997932</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205213</v>
+        <v>123205199</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500152</v>
+        <v>500157</v>
       </c>
       <c r="R10" t="n">
-        <v>6998004</v>
+        <v>6997979</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205198</v>
+        <v>123205211</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500158</v>
+        <v>500162</v>
       </c>
       <c r="R11" t="n">
-        <v>6997989</v>
+        <v>6998023</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205202</v>
+        <v>123205209</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500189</v>
+        <v>500274</v>
       </c>
       <c r="R12" t="n">
-        <v>6997952</v>
+        <v>6997998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205217</v>
+        <v>123205212</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499997</v>
+        <v>500164</v>
       </c>
       <c r="R13" t="n">
-        <v>6997980</v>
+        <v>6998017</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205209</v>
+        <v>123205214</v>
       </c>
       <c r="B14" t="n">
         <v>57481</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500274</v>
+        <v>500156</v>
       </c>
       <c r="R14" t="n">
-        <v>6997998</v>
+        <v>6998001</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205199</v>
+        <v>123205207</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500157</v>
+        <v>500272</v>
       </c>
       <c r="R15" t="n">
-        <v>6997979</v>
+        <v>6997930</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205212</v>
+        <v>123205210</v>
       </c>
       <c r="B16" t="n">
         <v>57481</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500164</v>
+        <v>500157</v>
       </c>
       <c r="R16" t="n">
-        <v>6998017</v>
+        <v>6998027</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205208</v>
+        <v>123205215</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500289</v>
+        <v>500160</v>
       </c>
       <c r="R17" t="n">
-        <v>6997933</v>
+        <v>6997999</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205206</v>
+        <v>123205201</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500253</v>
+        <v>500163</v>
       </c>
       <c r="R18" t="n">
-        <v>6997934</v>
+        <v>6997976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205204</v>
+        <v>123205213</v>
       </c>
       <c r="B19" t="n">
         <v>57481</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500241</v>
+        <v>500152</v>
       </c>
       <c r="R19" t="n">
-        <v>6997932</v>
+        <v>6998004</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205206</v>
+        <v>123205201</v>
       </c>
       <c r="B2" t="n">
         <v>57481</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500253</v>
+        <v>500163</v>
       </c>
       <c r="R2" t="n">
-        <v>6997934</v>
+        <v>6997976</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205198</v>
+        <v>123205204</v>
       </c>
       <c r="B4" t="n">
         <v>57481</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500158</v>
+        <v>500241</v>
       </c>
       <c r="R4" t="n">
-        <v>6997989</v>
+        <v>6997932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205208</v>
+        <v>123205206</v>
       </c>
       <c r="B5" t="n">
         <v>57481</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500289</v>
+        <v>500253</v>
       </c>
       <c r="R5" t="n">
-        <v>6997933</v>
+        <v>6997934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205205</v>
+        <v>123205210</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500249</v>
+        <v>500157</v>
       </c>
       <c r="R6" t="n">
-        <v>6997921</v>
+        <v>6998027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205202</v>
+        <v>123205217</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500189</v>
+        <v>499997</v>
       </c>
       <c r="R7" t="n">
-        <v>6997952</v>
+        <v>6997980</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205217</v>
+        <v>123205214</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499997</v>
+        <v>500156</v>
       </c>
       <c r="R8" t="n">
-        <v>6997980</v>
+        <v>6998001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205204</v>
+        <v>123205211</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500241</v>
+        <v>500162</v>
       </c>
       <c r="R9" t="n">
-        <v>6997932</v>
+        <v>6998023</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205199</v>
+        <v>123205198</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500157</v>
+        <v>500158</v>
       </c>
       <c r="R10" t="n">
-        <v>6997979</v>
+        <v>6997989</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205211</v>
+        <v>123205215</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500162</v>
+        <v>500160</v>
       </c>
       <c r="R11" t="n">
-        <v>6998023</v>
+        <v>6997999</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205209</v>
+        <v>123205205</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500274</v>
+        <v>500249</v>
       </c>
       <c r="R12" t="n">
-        <v>6997998</v>
+        <v>6997921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205214</v>
+        <v>123205207</v>
       </c>
       <c r="B14" t="n">
         <v>57481</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500156</v>
+        <v>500272</v>
       </c>
       <c r="R14" t="n">
-        <v>6998001</v>
+        <v>6997930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205207</v>
+        <v>123205199</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500272</v>
+        <v>500157</v>
       </c>
       <c r="R15" t="n">
-        <v>6997930</v>
+        <v>6997979</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205210</v>
+        <v>123205209</v>
       </c>
       <c r="B16" t="n">
         <v>57481</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500157</v>
+        <v>500274</v>
       </c>
       <c r="R16" t="n">
-        <v>6998027</v>
+        <v>6997998</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205215</v>
+        <v>123205202</v>
       </c>
       <c r="B17" t="n">
         <v>57481</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500160</v>
+        <v>500189</v>
       </c>
       <c r="R17" t="n">
-        <v>6997999</v>
+        <v>6997952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205201</v>
+        <v>123205208</v>
       </c>
       <c r="B18" t="n">
         <v>57481</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500163</v>
+        <v>500289</v>
       </c>
       <c r="R18" t="n">
-        <v>6997976</v>
+        <v>6997933</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205199</v>
+        <v>123205215</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500157</v>
+        <v>500160</v>
       </c>
       <c r="R2" t="n">
-        <v>6997979</v>
+        <v>6997999</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205207</v>
+        <v>123205205</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500272</v>
+        <v>500249</v>
       </c>
       <c r="R3" t="n">
-        <v>6997930</v>
+        <v>6997921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205210</v>
+        <v>123205206</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500157</v>
+        <v>500253</v>
       </c>
       <c r="R4" t="n">
-        <v>6998027</v>
+        <v>6997934</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205204</v>
+        <v>123205207</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500241</v>
+        <v>500272</v>
       </c>
       <c r="R5" t="n">
-        <v>6997932</v>
+        <v>6997930</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205205</v>
+        <v>123205202</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500249</v>
+        <v>500189</v>
       </c>
       <c r="R6" t="n">
-        <v>6997921</v>
+        <v>6997952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205198</v>
+        <v>123205212</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500158</v>
+        <v>500164</v>
       </c>
       <c r="R7" t="n">
-        <v>6997989</v>
+        <v>6998017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205211</v>
+        <v>123205217</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500162</v>
+        <v>499997</v>
       </c>
       <c r="R8" t="n">
-        <v>6998023</v>
+        <v>6997980</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205201</v>
+        <v>123205198</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500163</v>
+        <v>500158</v>
       </c>
       <c r="R9" t="n">
-        <v>6997976</v>
+        <v>6997989</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205212</v>
+        <v>123205199</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500164</v>
+        <v>500157</v>
       </c>
       <c r="R10" t="n">
-        <v>6998017</v>
+        <v>6997979</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205208</v>
+        <v>123205214</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500289</v>
+        <v>500156</v>
       </c>
       <c r="R11" t="n">
-        <v>6997933</v>
+        <v>6998001</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205206</v>
+        <v>123205204</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500253</v>
+        <v>500241</v>
       </c>
       <c r="R12" t="n">
-        <v>6997934</v>
+        <v>6997932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205209</v>
+        <v>123205208</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500274</v>
+        <v>500289</v>
       </c>
       <c r="R13" t="n">
-        <v>6997998</v>
+        <v>6997933</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205214</v>
+        <v>123205213</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500156</v>
+        <v>500152</v>
       </c>
       <c r="R14" t="n">
-        <v>6998001</v>
+        <v>6998004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205202</v>
+        <v>123205211</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500189</v>
+        <v>500162</v>
       </c>
       <c r="R15" t="n">
-        <v>6997952</v>
+        <v>6998023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205215</v>
+        <v>123205201</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500160</v>
+        <v>500163</v>
       </c>
       <c r="R16" t="n">
-        <v>6997999</v>
+        <v>6997976</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205203</v>
+        <v>123205210</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500221</v>
+        <v>500157</v>
       </c>
       <c r="R17" t="n">
-        <v>6997968</v>
+        <v>6998027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205213</v>
+        <v>123205209</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500152</v>
+        <v>500274</v>
       </c>
       <c r="R18" t="n">
-        <v>6998004</v>
+        <v>6997998</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205217</v>
+        <v>123205203</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>499997</v>
+        <v>500221</v>
       </c>
       <c r="R19" t="n">
-        <v>6997980</v>
+        <v>6997968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205215</v>
+        <v>123205203</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500160</v>
+        <v>500221</v>
       </c>
       <c r="R2" t="n">
-        <v>6997999</v>
+        <v>6997968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205205</v>
+        <v>123205198</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500249</v>
+        <v>500158</v>
       </c>
       <c r="R3" t="n">
-        <v>6997921</v>
+        <v>6997989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205206</v>
+        <v>123205210</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500253</v>
+        <v>500157</v>
       </c>
       <c r="R4" t="n">
-        <v>6997934</v>
+        <v>6998027</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205207</v>
+        <v>123205214</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500272</v>
+        <v>500156</v>
       </c>
       <c r="R5" t="n">
-        <v>6997930</v>
+        <v>6998001</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>123205202</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205212</v>
+        <v>123205208</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500164</v>
+        <v>500289</v>
       </c>
       <c r="R7" t="n">
-        <v>6998017</v>
+        <v>6997933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205217</v>
+        <v>123205209</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499997</v>
+        <v>500274</v>
       </c>
       <c r="R8" t="n">
-        <v>6997980</v>
+        <v>6997998</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205198</v>
+        <v>123205211</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500158</v>
+        <v>500162</v>
       </c>
       <c r="R9" t="n">
-        <v>6997989</v>
+        <v>6998023</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205199</v>
+        <v>123205201</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500157</v>
+        <v>500163</v>
       </c>
       <c r="R10" t="n">
-        <v>6997979</v>
+        <v>6997976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205214</v>
+        <v>123205212</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500156</v>
+        <v>500164</v>
       </c>
       <c r="R11" t="n">
-        <v>6998001</v>
+        <v>6998017</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205204</v>
+        <v>123205217</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500241</v>
+        <v>499997</v>
       </c>
       <c r="R12" t="n">
-        <v>6997932</v>
+        <v>6997980</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205208</v>
+        <v>123205207</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500289</v>
+        <v>500272</v>
       </c>
       <c r="R13" t="n">
-        <v>6997933</v>
+        <v>6997930</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205213</v>
+        <v>123205215</v>
       </c>
       <c r="B14" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500152</v>
+        <v>500160</v>
       </c>
       <c r="R14" t="n">
-        <v>6998004</v>
+        <v>6997999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205211</v>
+        <v>123205204</v>
       </c>
       <c r="B15" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500162</v>
+        <v>500241</v>
       </c>
       <c r="R15" t="n">
-        <v>6998023</v>
+        <v>6997932</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205201</v>
+        <v>123205206</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500163</v>
+        <v>500253</v>
       </c>
       <c r="R16" t="n">
-        <v>6997976</v>
+        <v>6997934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205210</v>
+        <v>123205199</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>500157</v>
       </c>
       <c r="R17" t="n">
-        <v>6998027</v>
+        <v>6997979</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205209</v>
+        <v>123205213</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500274</v>
+        <v>500152</v>
       </c>
       <c r="R18" t="n">
-        <v>6997998</v>
+        <v>6998004</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205203</v>
+        <v>123205205</v>
       </c>
       <c r="B19" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500221</v>
+        <v>500249</v>
       </c>
       <c r="R19" t="n">
-        <v>6997968</v>
+        <v>6997921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205203</v>
+        <v>123205211</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500221</v>
+        <v>500162</v>
       </c>
       <c r="R2" t="n">
-        <v>6997968</v>
+        <v>6998023</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205198</v>
+        <v>123205201</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500158</v>
+        <v>500163</v>
       </c>
       <c r="R3" t="n">
-        <v>6997989</v>
+        <v>6997976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205210</v>
+        <v>123205208</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500157</v>
+        <v>500289</v>
       </c>
       <c r="R4" t="n">
-        <v>6998027</v>
+        <v>6997933</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205214</v>
+        <v>123205215</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500156</v>
+        <v>500160</v>
       </c>
       <c r="R5" t="n">
-        <v>6998001</v>
+        <v>6997999</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205202</v>
+        <v>123205207</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500189</v>
+        <v>500272</v>
       </c>
       <c r="R6" t="n">
-        <v>6997952</v>
+        <v>6997930</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205208</v>
+        <v>123205202</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500289</v>
+        <v>500189</v>
       </c>
       <c r="R7" t="n">
-        <v>6997933</v>
+        <v>6997952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205209</v>
+        <v>123205205</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500274</v>
+        <v>500249</v>
       </c>
       <c r="R8" t="n">
-        <v>6997998</v>
+        <v>6997921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205211</v>
+        <v>123205206</v>
       </c>
       <c r="B9" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500162</v>
+        <v>500253</v>
       </c>
       <c r="R9" t="n">
-        <v>6998023</v>
+        <v>6997934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205201</v>
+        <v>123205203</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500163</v>
+        <v>500221</v>
       </c>
       <c r="R10" t="n">
-        <v>6997976</v>
+        <v>6997968</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205212</v>
+        <v>123205210</v>
       </c>
       <c r="B11" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500164</v>
+        <v>500157</v>
       </c>
       <c r="R11" t="n">
-        <v>6998017</v>
+        <v>6998027</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205217</v>
+        <v>123205204</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499997</v>
+        <v>500241</v>
       </c>
       <c r="R12" t="n">
-        <v>6997980</v>
+        <v>6997932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205207</v>
+        <v>123205209</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500272</v>
+        <v>500274</v>
       </c>
       <c r="R13" t="n">
-        <v>6997930</v>
+        <v>6997998</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205215</v>
+        <v>123205212</v>
       </c>
       <c r="B14" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500160</v>
+        <v>500164</v>
       </c>
       <c r="R14" t="n">
-        <v>6997999</v>
+        <v>6998017</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205204</v>
+        <v>123205199</v>
       </c>
       <c r="B15" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500241</v>
+        <v>500157</v>
       </c>
       <c r="R15" t="n">
-        <v>6997932</v>
+        <v>6997979</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205206</v>
+        <v>123205217</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500253</v>
+        <v>499997</v>
       </c>
       <c r="R16" t="n">
-        <v>6997934</v>
+        <v>6997980</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205199</v>
+        <v>123205213</v>
       </c>
       <c r="B17" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500157</v>
+        <v>500152</v>
       </c>
       <c r="R17" t="n">
-        <v>6997979</v>
+        <v>6998004</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205213</v>
+        <v>123205198</v>
       </c>
       <c r="B18" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500152</v>
+        <v>500158</v>
       </c>
       <c r="R18" t="n">
-        <v>6998004</v>
+        <v>6997989</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205205</v>
+        <v>123205214</v>
       </c>
       <c r="B19" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500249</v>
+        <v>500156</v>
       </c>
       <c r="R19" t="n">
-        <v>6997921</v>
+        <v>6998001</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205211</v>
+        <v>123205213</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500162</v>
+        <v>500152</v>
       </c>
       <c r="R2" t="n">
-        <v>6998023</v>
+        <v>6998004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205201</v>
+        <v>123205205</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500163</v>
+        <v>500249</v>
       </c>
       <c r="R3" t="n">
-        <v>6997976</v>
+        <v>6997921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205208</v>
+        <v>123205203</v>
       </c>
       <c r="B4" t="n">
         <v>57491</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500289</v>
+        <v>500221</v>
       </c>
       <c r="R4" t="n">
-        <v>6997933</v>
+        <v>6997968</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205215</v>
+        <v>123205210</v>
       </c>
       <c r="B5" t="n">
         <v>57491</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500160</v>
+        <v>500157</v>
       </c>
       <c r="R5" t="n">
-        <v>6997999</v>
+        <v>6998027</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205207</v>
+        <v>123205201</v>
       </c>
       <c r="B6" t="n">
         <v>57491</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500272</v>
+        <v>500163</v>
       </c>
       <c r="R6" t="n">
-        <v>6997930</v>
+        <v>6997976</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205202</v>
+        <v>123205198</v>
       </c>
       <c r="B7" t="n">
         <v>57491</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500189</v>
+        <v>500158</v>
       </c>
       <c r="R7" t="n">
-        <v>6997952</v>
+        <v>6997989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205205</v>
+        <v>123205214</v>
       </c>
       <c r="B8" t="n">
         <v>57491</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500249</v>
+        <v>500156</v>
       </c>
       <c r="R8" t="n">
-        <v>6997921</v>
+        <v>6998001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205206</v>
+        <v>123205202</v>
       </c>
       <c r="B9" t="n">
         <v>57491</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500253</v>
+        <v>500189</v>
       </c>
       <c r="R9" t="n">
-        <v>6997934</v>
+        <v>6997952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205203</v>
+        <v>123205211</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500221</v>
+        <v>500162</v>
       </c>
       <c r="R10" t="n">
-        <v>6997968</v>
+        <v>6998023</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205210</v>
+        <v>123205215</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500157</v>
+        <v>500160</v>
       </c>
       <c r="R11" t="n">
-        <v>6998027</v>
+        <v>6997999</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205204</v>
+        <v>123205206</v>
       </c>
       <c r="B12" t="n">
         <v>57491</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500241</v>
+        <v>500253</v>
       </c>
       <c r="R12" t="n">
-        <v>6997932</v>
+        <v>6997934</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205209</v>
+        <v>123205217</v>
       </c>
       <c r="B13" t="n">
         <v>57491</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500274</v>
+        <v>499997</v>
       </c>
       <c r="R13" t="n">
-        <v>6997998</v>
+        <v>6997980</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205212</v>
+        <v>123205207</v>
       </c>
       <c r="B14" t="n">
         <v>57491</v>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500164</v>
+        <v>500272</v>
       </c>
       <c r="R14" t="n">
-        <v>6998017</v>
+        <v>6997930</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205199</v>
+        <v>123205209</v>
       </c>
       <c r="B15" t="n">
         <v>57491</v>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500157</v>
+        <v>500274</v>
       </c>
       <c r="R15" t="n">
-        <v>6997979</v>
+        <v>6997998</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,7 +2173,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205217</v>
+        <v>123205199</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>499997</v>
+        <v>500157</v>
       </c>
       <c r="R16" t="n">
-        <v>6997980</v>
+        <v>6997979</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205213</v>
+        <v>123205204</v>
       </c>
       <c r="B17" t="n">
         <v>57491</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500152</v>
+        <v>500241</v>
       </c>
       <c r="R17" t="n">
-        <v>6998004</v>
+        <v>6997932</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205198</v>
+        <v>123205212</v>
       </c>
       <c r="B18" t="n">
         <v>57491</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500158</v>
+        <v>500164</v>
       </c>
       <c r="R18" t="n">
-        <v>6997989</v>
+        <v>6998017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205214</v>
+        <v>123205208</v>
       </c>
       <c r="B19" t="n">
         <v>57491</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500156</v>
+        <v>500289</v>
       </c>
       <c r="R19" t="n">
-        <v>6998001</v>
+        <v>6997933</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123205213</v>
+        <v>123205198</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500152</v>
+        <v>500158</v>
       </c>
       <c r="R2" t="n">
-        <v>6998004</v>
+        <v>6997989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123205205</v>
+        <v>123205199</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500249</v>
+        <v>500157</v>
       </c>
       <c r="R3" t="n">
-        <v>6997921</v>
+        <v>6997979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123205203</v>
+        <v>123205201</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500221</v>
+        <v>500163</v>
       </c>
       <c r="R4" t="n">
-        <v>6997968</v>
+        <v>6997976</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123205210</v>
+        <v>123205202</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500157</v>
+        <v>500189</v>
       </c>
       <c r="R5" t="n">
-        <v>6998027</v>
+        <v>6997952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123205201</v>
+        <v>123205203</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500163</v>
+        <v>500221</v>
       </c>
       <c r="R6" t="n">
-        <v>6997976</v>
+        <v>6997968</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123205198</v>
+        <v>123205204</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500158</v>
+        <v>500241</v>
       </c>
       <c r="R7" t="n">
-        <v>6997989</v>
+        <v>6997932</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123205214</v>
+        <v>123205205</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500156</v>
+        <v>500249</v>
       </c>
       <c r="R8" t="n">
-        <v>6998001</v>
+        <v>6997921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,15 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123205202</v>
+        <v>123205206</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500189</v>
+        <v>500253</v>
       </c>
       <c r="R9" t="n">
-        <v>6997952</v>
+        <v>6997934</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,15 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123205211</v>
+        <v>123205207</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500162</v>
+        <v>500272</v>
       </c>
       <c r="R10" t="n">
-        <v>6998023</v>
+        <v>6997930</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1566,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,15 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123205215</v>
+        <v>123205208</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500160</v>
+        <v>500289</v>
       </c>
       <c r="R11" t="n">
-        <v>6997999</v>
+        <v>6997933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,15 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123205206</v>
+        <v>123205209</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500253</v>
+        <v>500274</v>
       </c>
       <c r="R12" t="n">
-        <v>6997934</v>
+        <v>6997998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1770,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,15 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123205217</v>
+        <v>123205210</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499997</v>
+        <v>500157</v>
       </c>
       <c r="R13" t="n">
-        <v>6997980</v>
+        <v>6998027</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123205207</v>
+        <v>123205211</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500272</v>
+        <v>500162</v>
       </c>
       <c r="R14" t="n">
-        <v>6997930</v>
+        <v>6998023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +1974,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,15 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123205209</v>
+        <v>123205212</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500274</v>
+        <v>500164</v>
       </c>
       <c r="R15" t="n">
-        <v>6997998</v>
+        <v>6998017</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123205199</v>
+        <v>123205213</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500157</v>
+        <v>500152</v>
       </c>
       <c r="R16" t="n">
-        <v>6997979</v>
+        <v>6998004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123205204</v>
+        <v>123205214</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500241</v>
+        <v>500156</v>
       </c>
       <c r="R17" t="n">
-        <v>6997932</v>
+        <v>6998001</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,15 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123205212</v>
+        <v>123205215</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500164</v>
+        <v>500160</v>
       </c>
       <c r="R18" t="n">
-        <v>6998017</v>
+        <v>6997999</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,15 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123205208</v>
+        <v>123205216</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500289</v>
+        <v>500058</v>
       </c>
       <c r="R19" t="n">
-        <v>6997933</v>
+        <v>6998049</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2598,6 +2508,108 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123205217</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tjärnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>499997</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6997980</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54354-2024 artfynd.xlsx
+++ b/artfynd/A 54354-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205198</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205199</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205201</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205202</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205210</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205211</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205212</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205213</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205214</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205215</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205216</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205217</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205203</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205204</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205205</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205206</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205207</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,8 +2705,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123205209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>